--- a/checkpoints.xlsx
+++ b/checkpoints.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,47 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>kawanishi-noseguchi-station</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>川西能勢口駅</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県川西市栄町</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>34.8275522</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>135.4128791</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>assets/train-bird-thumb.jpg</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>movie/train-bird.mp4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>電車が鳥になって飛び立つチェックポイントです。ここに近づいてチェックインすると動画が再生されます。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/checkpoints.xlsx
+++ b/checkpoints.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -617,6 +617,47 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>takarazuka-station-water-server</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>宝塚駅のウォーターサーバー</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県宝塚市栄町二丁目</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>34.8116243</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>135.3402463</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>assets/water-server-horse-thumb.jpg</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>movie/water-server-horse.mp4</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>白いウォーターサーバーが馬型のロボットになるチェックポイントです。ここに近づいてチェックインすると動画が再生されます。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/checkpoints.xlsx
+++ b/checkpoints.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -658,6 +658,47 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>menoto-jinja-station</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>売布神社駅</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県宝塚市売布四丁目</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>34.8157929</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>135.3613299</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>assets/station-roof-melt-thumb.jpg</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>movie/station-roof-melt.mp4</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>駅の屋根と柱がぐにょぐにょ動き出すチェックポイントです。ここに近づいてチェックインすると動画が再生されます。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/checkpoints.xlsx
+++ b/checkpoints.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -699,6 +699,47 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>aste-kawanishi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>アステ川西</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>兵庫県川西市栄町</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>34.8265467</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>135.4126774</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>assets/aste-kawanishi-dome-thumb.jpg</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>movie/aste-kawanishi-dome.mp4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>中央のふわふわドームが動き出すチェックポイントです。ここに近づいてチェックインすると動画が再生されます。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
